--- a/artfynd/A 13625-2023 artfynd.xlsx
+++ b/artfynd/A 13625-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 13625-2023 artfynd.xlsx
+++ b/artfynd/A 13625-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3447,6 +3447,112 @@
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>114829478</v>
+      </c>
+      <c r="B25" t="n">
+        <v>77409</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>314</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vitskaftad svartspik</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis viridialba</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Kremp.) A.F.W.Schmidt</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Hållbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>437222</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7006603</v>
+      </c>
+      <c r="S25" t="n">
+        <v>50</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2023-06-14</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2023-06-14</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim, Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 13625-2023 artfynd.xlsx
+++ b/artfynd/A 13625-2023 artfynd.xlsx
@@ -3558,7 +3558,7 @@
         <v>120752403</v>
       </c>
       <c r="B26" t="n">
-        <v>79679</v>
+        <v>79682</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>

--- a/artfynd/A 13625-2023 artfynd.xlsx
+++ b/artfynd/A 13625-2023 artfynd.xlsx
@@ -3558,7 +3558,7 @@
         <v>120752403</v>
       </c>
       <c r="B26" t="n">
-        <v>79682</v>
+        <v>79685</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>

--- a/artfynd/A 13625-2023 artfynd.xlsx
+++ b/artfynd/A 13625-2023 artfynd.xlsx
@@ -3558,7 +3558,7 @@
         <v>120752403</v>
       </c>
       <c r="B26" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>

--- a/artfynd/A 13625-2023 artfynd.xlsx
+++ b/artfynd/A 13625-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>108718929</v>
+        <v>114829478</v>
       </c>
       <c r="B2" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>78350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sällsjön SÖ, Jmt</t>
+          <t>Hållbacken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>437265.8680240445</v>
+        <v>437222</v>
       </c>
       <c r="R2" t="n">
-        <v>7006294.56066131</v>
+        <v>7006603</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,27 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-05-03</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-05-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>ringhack</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,33 +757,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim, Hugo Ström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>108718925</v>
+        <v>120752403</v>
       </c>
       <c r="B3" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,41 +787,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sällsjön SÖ, Jmt</t>
+          <t>MD8:Åre, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>437441.8026971049</v>
+        <v>437627</v>
       </c>
       <c r="R3" t="n">
-        <v>7006433.882732502</v>
+        <v>7006408</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,27 +841,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-05-03</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-05-03</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ringhack</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,12 +871,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -920,12 +886,7 @@
         <v>108718923</v>
       </c>
       <c r="B4" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -957,10 +918,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>437693.1568600214</v>
+        <v>437693</v>
       </c>
       <c r="R4" t="n">
-        <v>7006333.720904024</v>
+        <v>7006334</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,19 +951,9 @@
           <t>2023-05-03</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-05-03</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,15 +980,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>108718934</v>
+        <v>108718925</v>
       </c>
       <c r="B5" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1073,10 +1019,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>437251.0097213153</v>
+        <v>437442</v>
       </c>
       <c r="R5" t="n">
-        <v>7006251.485929966</v>
+        <v>7006434</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,19 +1052,9 @@
           <t>2023-05-03</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-05-03</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1150,15 +1086,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>108718940</v>
+        <v>108718926</v>
       </c>
       <c r="B6" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,10 +1125,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>437142.4856154905</v>
+        <v>437430</v>
       </c>
       <c r="R6" t="n">
-        <v>7006787.91673798</v>
+        <v>7006421</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1227,19 +1158,9 @@
           <t>2023-05-03</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-05-03</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1271,15 +1192,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>108718930</v>
+        <v>108718927</v>
       </c>
       <c r="B7" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1315,10 +1231,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>437403.8165098006</v>
+        <v>437348</v>
       </c>
       <c r="R7" t="n">
-        <v>7006294.143844516</v>
+        <v>7006460</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1348,19 +1264,9 @@
           <t>2023-05-03</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-05-03</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1392,15 +1298,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>108718927</v>
+        <v>108718928</v>
       </c>
       <c r="B8" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1436,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>437347.3375837047</v>
+        <v>437260</v>
       </c>
       <c r="R8" t="n">
-        <v>7006460.555242279</v>
+        <v>7006319</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1469,24 +1370,14 @@
           <t>2023-05-03</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-05-03</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1513,15 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>108718949</v>
+        <v>108718929</v>
       </c>
       <c r="B9" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1557,10 +1443,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>437232.1395232935</v>
+        <v>437266</v>
       </c>
       <c r="R9" t="n">
-        <v>7006653.843598615</v>
+        <v>7006294</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1590,19 +1476,9 @@
           <t>2023-05-03</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-05-03</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1634,15 +1510,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>108718943</v>
+        <v>108718930</v>
       </c>
       <c r="B10" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1678,10 +1549,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>437156.0212149328</v>
+        <v>437404</v>
       </c>
       <c r="R10" t="n">
-        <v>7006739.780347738</v>
+        <v>7006294</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1711,19 +1582,9 @@
           <t>2023-05-03</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-05-03</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1755,15 +1616,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>108718928</v>
+        <v>108718932</v>
       </c>
       <c r="B11" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1799,10 +1655,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>437260.4723100049</v>
+        <v>437306</v>
       </c>
       <c r="R11" t="n">
-        <v>7006319.508680805</v>
+        <v>7006255</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1832,19 +1688,9 @@
           <t>2023-05-03</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-05-03</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1876,15 +1722,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>108718947</v>
+        <v>108718934</v>
       </c>
       <c r="B12" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,10 +1761,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>437196.0548698546</v>
+        <v>437251</v>
       </c>
       <c r="R12" t="n">
-        <v>7006728.614212831</v>
+        <v>7006251</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1953,24 +1794,14 @@
           <t>2023-05-03</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-05-03</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1997,15 +1828,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>108718926</v>
+        <v>108718936</v>
       </c>
       <c r="B13" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2041,10 +1867,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>437430.2372204551</v>
+        <v>437230</v>
       </c>
       <c r="R13" t="n">
-        <v>7006420.556342849</v>
+        <v>7006259</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2074,24 +1900,14 @@
           <t>2023-05-03</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-05-03</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2118,15 +1934,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>108718953</v>
+        <v>108718937</v>
       </c>
       <c r="B14" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2154,7 +1965,11 @@
       <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2162,10 +1977,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>438033.4045416421</v>
+        <v>437220</v>
       </c>
       <c r="R14" t="n">
-        <v>7006292.397694888</v>
+        <v>7006411</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2195,31 +2010,21 @@
           <t>2023-05-03</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-05-03</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ri</t>
         </is>
       </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG14" t="b">
         <v>0</v>
@@ -2239,15 +2044,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>108718948</v>
+        <v>108718938</v>
       </c>
       <c r="B15" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2283,10 +2083,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>437215.8330926147</v>
+        <v>437084</v>
       </c>
       <c r="R15" t="n">
-        <v>7006675.839449953</v>
+        <v>7006709</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2316,24 +2116,14 @@
           <t>2023-05-03</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-05-03</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2360,15 +2150,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>108718938</v>
+        <v>108718939</v>
       </c>
       <c r="B16" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2404,10 +2189,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>437083.5155771806</v>
+        <v>437093</v>
       </c>
       <c r="R16" t="n">
-        <v>7006709.125224494</v>
+        <v>7006699</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2437,24 +2222,14 @@
           <t>2023-05-03</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-05-03</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2481,15 +2256,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>108718939</v>
+        <v>108718940</v>
       </c>
       <c r="B17" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2525,10 +2295,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>437092.8160429197</v>
+        <v>437142</v>
       </c>
       <c r="R17" t="n">
-        <v>7006699.008007247</v>
+        <v>7006788</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2558,24 +2328,14 @@
           <t>2023-05-03</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-05-03</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2602,15 +2362,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>108718950</v>
+        <v>108718941</v>
       </c>
       <c r="B18" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2646,10 +2401,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>437330.4075466889</v>
+        <v>437150</v>
       </c>
       <c r="R18" t="n">
-        <v>7006637.031554679</v>
+        <v>7006792</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2679,24 +2434,14 @@
           <t>2023-05-03</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-05-03</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2723,15 +2468,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>108718941</v>
+        <v>108718943</v>
       </c>
       <c r="B19" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2767,10 +2507,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>437149.3458266784</v>
+        <v>437156</v>
       </c>
       <c r="R19" t="n">
-        <v>7006791.847929343</v>
+        <v>7006740</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2800,19 +2540,9 @@
           <t>2023-05-03</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-05-03</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2847,12 +2577,7 @@
         <v>108718944</v>
       </c>
       <c r="B20" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2888,10 +2613,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>437153.3087088031</v>
+        <v>437153</v>
       </c>
       <c r="R20" t="n">
-        <v>7006739.833113052</v>
+        <v>7006740</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2921,19 +2646,9 @@
           <t>2023-05-03</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-05-03</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2965,15 +2680,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>108718952</v>
+        <v>108718946</v>
       </c>
       <c r="B21" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3009,10 +2719,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>437864.8221849522</v>
+        <v>437193</v>
       </c>
       <c r="R21" t="n">
-        <v>7006346.224326964</v>
+        <v>7006730</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3042,19 +2752,9 @@
           <t>2023-05-03</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2023-05-03</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3086,15 +2786,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>108718946</v>
+        <v>108718947</v>
       </c>
       <c r="B22" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3130,10 +2825,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>437193.3774615529</v>
+        <v>437196</v>
       </c>
       <c r="R22" t="n">
-        <v>7006730.472810662</v>
+        <v>7006728</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3163,24 +2858,14 @@
           <t>2023-05-03</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2023-05-03</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3207,15 +2892,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>108718932</v>
+        <v>108718948</v>
       </c>
       <c r="B23" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3251,10 +2931,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>437306.259954496</v>
+        <v>437216</v>
       </c>
       <c r="R23" t="n">
-        <v>7006254.930521684</v>
+        <v>7006676</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3284,19 +2964,9 @@
           <t>2023-05-03</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2023-05-03</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3328,15 +2998,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>108718951</v>
+        <v>108718949</v>
       </c>
       <c r="B24" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3372,10 +3037,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>437349.3470597818</v>
+        <v>437232</v>
       </c>
       <c r="R24" t="n">
-        <v>7006727.444441697</v>
+        <v>7006654</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3405,19 +3070,9 @@
           <t>2023-05-03</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2023-05-03</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3449,15 +3104,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>114829478</v>
+        <v>108718950</v>
       </c>
       <c r="B25" t="n">
-        <v>77463</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3465,40 +3115,41 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>314</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Hållbacken, Jmt</t>
+          <t>Sällsjön SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>437222</v>
+        <v>437330</v>
       </c>
       <c r="R25" t="n">
-        <v>7006603</v>
+        <v>7006637</v>
       </c>
       <c r="S25" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3522,12 +3173,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-05-03</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-06-14</t>
+          <t>2023-05-03</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3536,34 +3192,28 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Hugo Ström, Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120752403</v>
+        <v>108718951</v>
       </c>
       <c r="B26" t="n">
-        <v>79688</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3571,37 +3221,41 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>MD8:Åre, SE-JA, SE, Jmt</t>
+          <t>Sällsjön SÖ, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>437627</v>
+        <v>437349</v>
       </c>
       <c r="R26" t="n">
-        <v>7006408</v>
+        <v>7006727</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3625,22 +3279,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>11:11</t>
+          <t>2023-05-03</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>11:11</t>
+          <t>2023-05-03</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3655,15 +3304,227 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>108718952</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Sällsjön SÖ, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>437865</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7006346</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2023-05-03</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2023-05-03</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>108718953</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Sällsjön SÖ, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>438034</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7006292</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2023-05-03</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2023-05-03</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13625-2023 artfynd.xlsx
+++ b/artfynd/A 13625-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AZ28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114829478</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120752403</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -977,6 +992,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108718923</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1083,6 +1103,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108718925</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1189,6 +1214,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108718926</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1295,6 +1325,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108718927</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1401,6 +1436,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108718928</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1507,6 +1547,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108718929</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1613,6 +1658,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108718930</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1719,6 +1769,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108718932</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1825,6 +1880,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108718934</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1931,6 +1991,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108718936</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2041,6 +2106,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108718937</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2147,6 +2217,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108718938</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2253,6 +2328,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108718939</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2359,6 +2439,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108718940</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2465,6 +2550,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108718941</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2571,6 +2661,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108718943</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2677,6 +2772,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108718944</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2783,6 +2883,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108718946</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2889,6 +2994,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108718947</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2995,6 +3105,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108718948</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3101,6 +3216,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108718949</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3207,6 +3327,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108718950</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3313,6 +3438,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108718951</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3419,6 +3549,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108718952</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3525,8 +3660,42 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108718953</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>